--- a/data/base/Backlog_14.xlsx
+++ b/data/base/Backlog_14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{245291F2-A5C7-49D0-9437-7B9E87CA767B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B3A1B46-AEC0-4CCA-8051-9FFCE0F72D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="30">
   <si>
     <t>Status</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>Michel Pessoa</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -707,7 +710,7 @@
         <v>46125</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>14</v>
@@ -742,7 +745,7 @@
         <v>46125</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>14</v>
@@ -853,7 +856,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1">
         <v>2026</v>
@@ -868,7 +871,7 @@
         <v>46129</v>
       </c>
       <c r="G2" s="6">
-        <v>9411</v>
+        <v>14389</v>
       </c>
       <c r="H2" s="13">
         <v>46045.666400462964</v>
@@ -888,7 +891,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1">
         <v>2026</v>
@@ -903,7 +906,7 @@
         <v>46129</v>
       </c>
       <c r="G3" s="6">
-        <v>13435</v>
+        <v>14441</v>
       </c>
       <c r="H3" s="13">
         <v>46105.607372685183</v>
@@ -912,7 +915,7 @@
         <v>46125</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>1</v>
@@ -923,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
         <v>2026</v>
@@ -938,7 +941,7 @@
         <v>46129</v>
       </c>
       <c r="G4" s="6">
-        <v>13446</v>
+        <v>14467</v>
       </c>
       <c r="H4" s="13">
         <v>46105.680798611109</v>
@@ -958,7 +961,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1">
         <v>2026</v>
@@ -973,7 +976,7 @@
         <v>46129</v>
       </c>
       <c r="G5" s="6">
-        <v>13876</v>
+        <v>14494</v>
       </c>
       <c r="H5" s="13">
         <v>46112.694756944446</v>
@@ -982,7 +985,7 @@
         <v>46125</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -993,7 +996,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1">
         <v>2026</v>
@@ -1008,7 +1011,7 @@
         <v>46129</v>
       </c>
       <c r="G6" s="6">
-        <v>14030</v>
+        <v>14525</v>
       </c>
       <c r="H6" s="13">
         <v>46113.568472222221</v>
@@ -1017,7 +1020,7 @@
         <v>46125</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>1</v>
@@ -1043,7 +1046,7 @@
         <v>46129</v>
       </c>
       <c r="G7" s="6">
-        <v>14091</v>
+        <v>9411</v>
       </c>
       <c r="H7" s="13">
         <v>46115.662233796298</v>
@@ -1063,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
         <v>2026</v>
@@ -1078,7 +1081,7 @@
         <v>46129</v>
       </c>
       <c r="G8" s="6">
-        <v>14098</v>
+        <v>14091</v>
       </c>
       <c r="H8" s="13">
         <v>46115.438043981485</v>
@@ -1087,7 +1090,7 @@
         <v>46125</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>1</v>
@@ -1098,7 +1101,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C9" s="1">
         <v>2026</v>
@@ -1113,7 +1116,7 @@
         <v>46129</v>
       </c>
       <c r="G9" s="6">
-        <v>14130</v>
+        <v>14136</v>
       </c>
       <c r="H9" s="13">
         <v>46115.640659722223</v>
@@ -1122,7 +1125,7 @@
         <v>46125</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>1</v>
@@ -1133,7 +1136,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1">
         <v>2026</v>
@@ -1148,7 +1151,7 @@
         <v>46129</v>
       </c>
       <c r="G10" s="6">
-        <v>14136</v>
+        <v>13435</v>
       </c>
       <c r="H10" s="13">
         <v>46118.565335648149</v>
@@ -1168,7 +1171,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1">
         <v>2026</v>
@@ -1183,7 +1186,7 @@
         <v>46129</v>
       </c>
       <c r="G11" s="6">
-        <v>14145</v>
+        <v>13446</v>
       </c>
       <c r="H11" s="13">
         <v>46115.583333333336</v>
@@ -1203,7 +1206,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1">
         <v>2026</v>
@@ -1218,7 +1221,7 @@
         <v>46129</v>
       </c>
       <c r="G12" s="6">
-        <v>14204</v>
+        <v>14409</v>
       </c>
       <c r="H12" s="13">
         <v>46118.492581018516</v>
@@ -1238,7 +1241,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1">
         <v>2026</v>
@@ -1253,7 +1256,7 @@
         <v>46129</v>
       </c>
       <c r="G13" s="6">
-        <v>14250</v>
+        <v>14431</v>
       </c>
       <c r="H13" s="13">
         <v>46119.451284722221</v>
@@ -1273,7 +1276,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C14" s="1">
         <v>2026</v>
@@ -1288,7 +1291,7 @@
         <v>46129</v>
       </c>
       <c r="G14" s="6">
-        <v>14372</v>
+        <v>14098</v>
       </c>
       <c r="H14" s="13">
         <v>46121.459606481483</v>
@@ -1308,7 +1311,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
         <v>2026</v>
@@ -1323,7 +1326,7 @@
         <v>46129</v>
       </c>
       <c r="G15" s="6">
-        <v>14389</v>
+        <v>14145</v>
       </c>
       <c r="H15" s="13">
         <v>46121.571192129632</v>
@@ -1378,7 +1381,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>2026</v>
@@ -1393,7 +1396,7 @@
         <v>46129</v>
       </c>
       <c r="G17" s="6">
-        <v>14409</v>
+        <v>14204</v>
       </c>
       <c r="H17" s="13">
         <v>46121.532824074071</v>
@@ -1413,7 +1416,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="1">
         <v>2026</v>
@@ -1428,7 +1431,7 @@
         <v>46129</v>
       </c>
       <c r="G18" s="6">
-        <v>14431</v>
+        <v>14250</v>
       </c>
       <c r="H18" s="13">
         <v>46121.583333333336</v>
@@ -1437,7 +1440,7 @@
         <v>46125</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>1</v>
@@ -1448,7 +1451,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" s="1">
         <v>2026</v>
@@ -1463,7 +1466,7 @@
         <v>46129</v>
       </c>
       <c r="G19" s="6">
-        <v>14441</v>
+        <v>14449</v>
       </c>
       <c r="H19" s="13">
         <v>46122.387361111112</v>
@@ -1483,7 +1486,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1">
         <v>2026</v>
@@ -1498,7 +1501,7 @@
         <v>46129</v>
       </c>
       <c r="G20" s="6">
-        <v>14449</v>
+        <v>14372</v>
       </c>
       <c r="H20" s="13">
         <v>46122.408472222225</v>
@@ -1518,7 +1521,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1">
         <v>2026</v>
@@ -1533,7 +1536,7 @@
         <v>46129</v>
       </c>
       <c r="G21" s="6">
-        <v>14467</v>
+        <v>13876</v>
       </c>
       <c r="H21" s="13">
         <v>46122.400868055556</v>
@@ -1553,7 +1556,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1">
         <v>2026</v>
@@ -1568,7 +1571,7 @@
         <v>46129</v>
       </c>
       <c r="G22" s="6">
-        <v>14468</v>
+        <v>14130</v>
       </c>
       <c r="H22" s="13">
         <v>46122.526701388888</v>
@@ -1588,7 +1591,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1">
         <v>2026</v>
@@ -1603,7 +1606,7 @@
         <v>46129</v>
       </c>
       <c r="G23" s="6">
-        <v>14494</v>
+        <v>14535</v>
       </c>
       <c r="H23" s="13">
         <v>46122.685057870367</v>
@@ -1612,7 +1615,7 @@
         <v>46125</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>1</v>
@@ -1638,7 +1641,7 @@
         <v>46129</v>
       </c>
       <c r="G24" s="6">
-        <v>14497</v>
+        <v>14030</v>
       </c>
       <c r="H24" s="13">
         <v>46122.69494212963</v>
@@ -1647,7 +1650,7 @@
         <v>46125</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>1</v>
@@ -1673,7 +1676,7 @@
         <v>46129</v>
       </c>
       <c r="G25" s="6">
-        <v>14518</v>
+        <v>14468</v>
       </c>
       <c r="H25" s="13">
         <v>46125.342673611114</v>
@@ -1682,7 +1685,7 @@
         <v>46125</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>1</v>
@@ -1693,7 +1696,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C26" s="1">
         <v>2026</v>
@@ -1708,7 +1711,7 @@
         <v>46129</v>
       </c>
       <c r="G26" s="6">
-        <v>14525</v>
+        <v>14497</v>
       </c>
       <c r="H26" s="13">
         <v>46122.653645833336</v>
@@ -1728,7 +1731,7 @@
         <v>17</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C27" s="1">
         <v>2026</v>
@@ -1743,7 +1746,7 @@
         <v>46129</v>
       </c>
       <c r="G27" s="6">
-        <v>14535</v>
+        <v>14518</v>
       </c>
       <c r="H27" s="13">
         <v>46125.454861111109</v>
@@ -1787,7 +1790,7 @@
         <v>46125</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>1</v>
@@ -1795,7 +1798,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{A01383FE-69B8-4AB3-AF26-C199A6A7A8A1}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G28">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
